--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4755-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4755-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4909EEFB-36FA-4B3E-82B9-C469C65A45CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA52951B-3ACD-4F37-9A6D-E8EB5AF8A83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{13353FE6-DFB3-494C-8F1F-420468162E89}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{4CE49C79-3BAB-4028-BE2C-AE3C74B8062A}"/>
   </bookViews>
   <sheets>
     <sheet name="4755-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1576,24 +1576,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F6FDAC-A8D2-4228-933D-FBBDF7F0AC58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853957B1-1D4F-467E-B774-4AB4D08C3BDA}">
   <dimension ref="A1:R60"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1621,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1651,7 +1651,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1747,7 +1747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1827,7 +1827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>2025</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2024</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>2023</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>26</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>26</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>26</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>26</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2022</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2021</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>26</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>26</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="51">
         <v>2020</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>26</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>26</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>26</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>26</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="49">
         <v>2019</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>26</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>26</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>26</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="51">
         <v>2018</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="49">
         <v>2017</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="51">
         <v>2016</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="49">
         <v>2015</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="51">
         <v>2014</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="49">
         <v>2013</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="51" t="s">
         <v>63</v>
       </c>
